--- a/tests/assets/golden/win32com/test_template_2_charts_filled.xlsx
+++ b/tests/assets/golden/win32com/test_template_2_charts_filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\xlfill\tests\assets\golden\win32com\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\fillxl\tests\assets\golden\win32com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08887259-6F8D-4C4A-9E45-9B2C49421727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8D26E57-D16D-4D27-B078-D89E56EC2E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,11 +241,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1411,7 +1412,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000001-2559-4067-A3F2-6DC6207159D0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1431,7 +1432,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000003-2559-4067-A3F2-6DC6207159D0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1451,7 +1452,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000005-2559-4067-A3F2-6DC6207159D0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1471,7 +1472,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000007-2559-4067-A3F2-6DC6207159D0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3087,7 +3088,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000001-E737-4BAE-B62D-B485C790A9DD}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3107,7 +3108,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000003-E737-4BAE-B62D-B485C790A9DD}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3127,7 +3128,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000005-E737-4BAE-B62D-B485C790A9DD}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3147,7 +3148,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000007-E737-4BAE-B62D-B485C790A9DD}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10776,7 +10777,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="2">
@@ -10793,7 +10794,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="2">
@@ -10810,7 +10811,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="2">
@@ -10859,7 +10860,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="2">
@@ -10867,7 +10868,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="2">
@@ -10875,7 +10876,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B4" s="2">
@@ -10883,7 +10884,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="2">
@@ -11038,7 +11039,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="1">
@@ -11046,7 +11047,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="1">
@@ -11054,7 +11055,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="1">
@@ -11062,7 +11063,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B5" s="1">
@@ -11102,7 +11103,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="2">
@@ -11110,7 +11111,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="2">
@@ -11118,7 +11119,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="2">
@@ -11172,7 +11173,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="2">
@@ -11186,7 +11187,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="2">
@@ -11200,7 +11201,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B4" s="2">
@@ -11214,7 +11215,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="2">
@@ -11278,7 +11279,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="2">
@@ -11289,7 +11290,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="2">
@@ -11300,7 +11301,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B4" s="2">
@@ -11311,7 +11312,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="2">
@@ -11371,7 +11372,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2">
@@ -11379,7 +11380,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2">
@@ -11387,7 +11388,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="2">
@@ -11395,7 +11396,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B5" s="2">
@@ -11445,7 +11446,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B2" s="2">
@@ -11462,7 +11463,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="2">

--- a/tests/assets/golden/win32com/test_template_2_charts_filled.xlsx
+++ b/tests/assets/golden/win32com/test_template_2_charts_filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\fillxl\tests\assets\golden\win32com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8D26E57-D16D-4D27-B078-D89E56EC2E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15F44317-6C43-4292-8682-5C07EEF62AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,75 +251,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1412,7 +1349,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-2559-4067-A3F2-6DC6207159D0}"/>
+                <c16:uniqueId val="{00000001-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1432,7 +1369,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-2559-4067-A3F2-6DC6207159D0}"/>
+                <c16:uniqueId val="{00000003-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1452,7 +1389,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-2559-4067-A3F2-6DC6207159D0}"/>
+                <c16:uniqueId val="{00000005-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1472,7 +1409,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-2559-4067-A3F2-6DC6207159D0}"/>
+                <c16:uniqueId val="{00000007-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3088,7 +3025,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E737-4BAE-B62D-B485C790A9DD}"/>
+                <c16:uniqueId val="{00000001-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3108,7 +3045,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E737-4BAE-B62D-B485C790A9DD}"/>
+                <c16:uniqueId val="{00000003-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3128,7 +3065,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E737-4BAE-B62D-B485C790A9DD}"/>
+                <c16:uniqueId val="{00000005-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3148,7 +3085,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-E737-4BAE-B62D-B485C790A9DD}"/>
+                <c16:uniqueId val="{00000007-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10377,10 +10314,10 @@
   <autoFilter ref="A1:E4" xr:uid="{F9759E1A-E769-4503-ACAA-75E734E1019E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F64937E1-3CAB-49B3-9969-49EB64D48CE0}" name="Region"/>
-    <tableColumn id="2" xr3:uid="{F28EF62F-EC59-4BDA-8297-EE689B032D5D}" name="Q1" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{0941B66B-7629-4FEC-801D-FC69BC1BC41E}" name="Q2" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{11435206-3A7A-4394-AC0E-C68226CC2639}" name="Q3" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{9ED417C5-8EAF-4DE2-AACA-CFE24A4F6ADB}" name="Q4" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{F28EF62F-EC59-4BDA-8297-EE689B032D5D}" name="Q1"/>
+    <tableColumn id="3" xr3:uid="{0941B66B-7629-4FEC-801D-FC69BC1BC41E}" name="Q2"/>
+    <tableColumn id="4" xr3:uid="{11435206-3A7A-4394-AC0E-C68226CC2639}" name="Q3"/>
+    <tableColumn id="5" xr3:uid="{9ED417C5-8EAF-4DE2-AACA-CFE24A4F6ADB}" name="Q4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10391,7 +10328,7 @@
   <autoFilter ref="A1:B5" xr:uid="{271571DB-E354-486D-8BA9-CBD0925FE064}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{AC5D3C91-00CF-41E9-B566-E4BD0E90A761}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{282D96EB-44D7-41FF-BBBA-00A6DFD0AEEA}" name="Amount" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{282D96EB-44D7-41FF-BBBA-00A6DFD0AEEA}" name="Amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10401,9 +10338,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{88FC00A3-2A48-465E-BD27-96CD5D759FDE}" name="LineChartTable" displayName="LineChartTable" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5" xr:uid="{88FC00A3-2A48-465E-BD27-96CD5D759FDE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F219D7EB-B5A1-420C-83AA-53EFD3121A68}" name="Date" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4172356F-0AE0-4831-A28A-35681C8686FD}" name="2024" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{8F9BF938-40DE-49CE-B285-6B29FAF7577C}" name="2025" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{F219D7EB-B5A1-420C-83AA-53EFD3121A68}" name="Date" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4172356F-0AE0-4831-A28A-35681C8686FD}" name="2024"/>
+    <tableColumn id="3" xr3:uid="{8F9BF938-40DE-49CE-B285-6B29FAF7577C}" name="2025"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10414,7 +10351,7 @@
   <autoFilter ref="A1:B5" xr:uid="{5511B15F-C72D-4CAF-8BAC-B40DF37D387F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{0948B983-5D2E-4009-A288-36B6C88966F2}" name="Company"/>
-    <tableColumn id="2" xr3:uid="{CDBC8D6C-D2C8-42DE-89A6-00F038CDA092}" name="Market Share" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{CDBC8D6C-D2C8-42DE-89A6-00F038CDA092}" name="Market Share"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10425,7 +10362,7 @@
   <autoFilter ref="A1:B4" xr:uid="{9745E24B-ECDB-4E01-8397-80AA2E17D4BD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{0DD5BCF3-1409-4D5D-AA68-9444817027B4}" name="Department"/>
-    <tableColumn id="2" xr3:uid="{81253001-31E1-4024-ACB6-6B51C663A873}" name="Employees" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{81253001-31E1-4024-ACB6-6B51C663A873}" name="Employees"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10436,9 +10373,9 @@
   <autoFilter ref="A1:D5" xr:uid="{E5DBD958-C0FB-4127-BA84-9AF3BEEE2FC8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{9C222393-3686-447D-B63A-77E85CFCD4CC}" name="Week"/>
-    <tableColumn id="2" xr3:uid="{8C6D3BF1-6981-4653-A332-0EA70FE4DF32}" name="Desktop" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{58323AFF-7714-4630-B93B-8BA929CEBF83}" name="Mobile" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{17C2F12F-0E3C-48C1-992F-01189A10861D}" name="Tablet" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{8C6D3BF1-6981-4653-A332-0EA70FE4DF32}" name="Desktop"/>
+    <tableColumn id="3" xr3:uid="{58323AFF-7714-4630-B93B-8BA929CEBF83}" name="Mobile"/>
+    <tableColumn id="4" xr3:uid="{17C2F12F-0E3C-48C1-992F-01189A10861D}" name="Tablet"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10449,8 +10386,8 @@
   <autoFilter ref="A1:C5" xr:uid="{44046314-B45D-4FBD-AB59-40E215828895}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3D76B09E-61B3-48CE-8430-EA93A493F6D4}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{7E5DC835-FA63-49B4-9E41-63B34787F5F9}" name="Price ($)" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{6DF38014-2A3F-48C0-AFD1-C97F0DA9FAC4}" name="Units Sold" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{7E5DC835-FA63-49B4-9E41-63B34787F5F9}" name="Price ($)"/>
+    <tableColumn id="3" xr3:uid="{6DF38014-2A3F-48C0-AFD1-C97F0DA9FAC4}" name="Units Sold"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10461,7 +10398,7 @@
   <autoFilter ref="A1:B5" xr:uid="{854184C0-11BE-470B-9AAE-8D996C01FD75}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{93981815-9F52-44D0-B0AD-000D0A261264}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{52CBAC57-9BC2-4F24-95F2-2570BC7F99AF}" name="Budget" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{52CBAC57-9BC2-4F24-95F2-2570BC7F99AF}" name="Budget"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10472,10 +10409,10 @@
   <autoFilter ref="A1:E3" xr:uid="{BFD98620-53F4-4A7B-917E-2F2D07544F17}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{25E65101-623A-4E97-9D4F-C991AF81A253}" name="Quarter"/>
-    <tableColumn id="2" xr3:uid="{C866BA2B-9180-4651-95FF-9AF2EA1AA03B}" name="Electronics" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{000C1675-EE8A-48C7-A119-17BD973C3F4B}" name="Clothing" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{589F7E3E-A5A7-4C98-8453-7D82E0E107A7}" name="Food" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{6D414AF1-3518-45F2-BC6C-DAAA0B7DE738}" name="Home" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{C866BA2B-9180-4651-95FF-9AF2EA1AA03B}" name="Electronics"/>
+    <tableColumn id="3" xr3:uid="{000C1675-EE8A-48C7-A119-17BD973C3F4B}" name="Clothing"/>
+    <tableColumn id="4" xr3:uid="{589F7E3E-A5A7-4C98-8453-7D82E0E107A7}" name="Food"/>
+    <tableColumn id="5" xr3:uid="{6D414AF1-3518-45F2-BC6C-DAAA0B7DE738}" name="Home"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10485,9 +10422,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{EA414483-F9F2-4B7E-B644-37C58CF9DDFA}" name="ComboChartTable" displayName="ComboChartTable" ref="A1:C4" totalsRowShown="0">
   <autoFilter ref="A1:C4" xr:uid="{EA414483-F9F2-4B7E-B644-37C58CF9DDFA}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8646F911-3A34-4300-BA20-C9CC02C005D1}" name="Date" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{7417EAA7-6F9C-4AFC-A5E9-2EBA455D02B3}" name="Revenue" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{67872E29-B587-4821-8CF2-1DF062546030}" name="Growth Rate" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8646F911-3A34-4300-BA20-C9CC02C005D1}" name="Date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{7417EAA7-6F9C-4AFC-A5E9-2EBA455D02B3}" name="Revenue"/>
+    <tableColumn id="3" xr3:uid="{67872E29-B587-4821-8CF2-1DF062546030}" name="Growth Rate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/tests/assets/golden/win32com/test_template_2_charts_filled.xlsx
+++ b/tests/assets/golden/win32com/test_template_2_charts_filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\xlfill\tests\assets\golden\win32com\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\fillxl\tests\assets\golden\win32com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08887259-6F8D-4C4A-9E45-9B2C49421727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15F44317-6C43-4292-8682-5C07EEF62AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,84 +241,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1411,7 +1349,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000001-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1431,7 +1369,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000003-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1451,7 +1389,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000005-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1471,7 +1409,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-969B-4DE8-B3E5-6A109F13B981}"/>
+                <c16:uniqueId val="{00000007-C9DA-4A24-8A75-3E88FF04134C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3087,7 +3025,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000001-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3107,7 +3045,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000003-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3127,7 +3065,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000005-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3147,7 +3085,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-FE79-400D-B732-6459FB78363E}"/>
+                <c16:uniqueId val="{00000007-64E5-4A2D-939B-60A2AD82A03A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -10376,10 +10314,10 @@
   <autoFilter ref="A1:E4" xr:uid="{F9759E1A-E769-4503-ACAA-75E734E1019E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F64937E1-3CAB-49B3-9969-49EB64D48CE0}" name="Region"/>
-    <tableColumn id="2" xr3:uid="{F28EF62F-EC59-4BDA-8297-EE689B032D5D}" name="Q1" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{0941B66B-7629-4FEC-801D-FC69BC1BC41E}" name="Q2" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{11435206-3A7A-4394-AC0E-C68226CC2639}" name="Q3" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{9ED417C5-8EAF-4DE2-AACA-CFE24A4F6ADB}" name="Q4" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{F28EF62F-EC59-4BDA-8297-EE689B032D5D}" name="Q1"/>
+    <tableColumn id="3" xr3:uid="{0941B66B-7629-4FEC-801D-FC69BC1BC41E}" name="Q2"/>
+    <tableColumn id="4" xr3:uid="{11435206-3A7A-4394-AC0E-C68226CC2639}" name="Q3"/>
+    <tableColumn id="5" xr3:uid="{9ED417C5-8EAF-4DE2-AACA-CFE24A4F6ADB}" name="Q4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10390,7 +10328,7 @@
   <autoFilter ref="A1:B5" xr:uid="{271571DB-E354-486D-8BA9-CBD0925FE064}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{AC5D3C91-00CF-41E9-B566-E4BD0E90A761}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{282D96EB-44D7-41FF-BBBA-00A6DFD0AEEA}" name="Amount" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{282D96EB-44D7-41FF-BBBA-00A6DFD0AEEA}" name="Amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10400,9 +10338,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{88FC00A3-2A48-465E-BD27-96CD5D759FDE}" name="LineChartTable" displayName="LineChartTable" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5" xr:uid="{88FC00A3-2A48-465E-BD27-96CD5D759FDE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F219D7EB-B5A1-420C-83AA-53EFD3121A68}" name="Date" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4172356F-0AE0-4831-A28A-35681C8686FD}" name="2024" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{8F9BF938-40DE-49CE-B285-6B29FAF7577C}" name="2025" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{F219D7EB-B5A1-420C-83AA-53EFD3121A68}" name="Date" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4172356F-0AE0-4831-A28A-35681C8686FD}" name="2024"/>
+    <tableColumn id="3" xr3:uid="{8F9BF938-40DE-49CE-B285-6B29FAF7577C}" name="2025"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10413,7 +10351,7 @@
   <autoFilter ref="A1:B5" xr:uid="{5511B15F-C72D-4CAF-8BAC-B40DF37D387F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{0948B983-5D2E-4009-A288-36B6C88966F2}" name="Company"/>
-    <tableColumn id="2" xr3:uid="{CDBC8D6C-D2C8-42DE-89A6-00F038CDA092}" name="Market Share" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{CDBC8D6C-D2C8-42DE-89A6-00F038CDA092}" name="Market Share"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10424,7 +10362,7 @@
   <autoFilter ref="A1:B4" xr:uid="{9745E24B-ECDB-4E01-8397-80AA2E17D4BD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{0DD5BCF3-1409-4D5D-AA68-9444817027B4}" name="Department"/>
-    <tableColumn id="2" xr3:uid="{81253001-31E1-4024-ACB6-6B51C663A873}" name="Employees" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{81253001-31E1-4024-ACB6-6B51C663A873}" name="Employees"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10435,9 +10373,9 @@
   <autoFilter ref="A1:D5" xr:uid="{E5DBD958-C0FB-4127-BA84-9AF3BEEE2FC8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{9C222393-3686-447D-B63A-77E85CFCD4CC}" name="Week"/>
-    <tableColumn id="2" xr3:uid="{8C6D3BF1-6981-4653-A332-0EA70FE4DF32}" name="Desktop" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{58323AFF-7714-4630-B93B-8BA929CEBF83}" name="Mobile" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{17C2F12F-0E3C-48C1-992F-01189A10861D}" name="Tablet" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{8C6D3BF1-6981-4653-A332-0EA70FE4DF32}" name="Desktop"/>
+    <tableColumn id="3" xr3:uid="{58323AFF-7714-4630-B93B-8BA929CEBF83}" name="Mobile"/>
+    <tableColumn id="4" xr3:uid="{17C2F12F-0E3C-48C1-992F-01189A10861D}" name="Tablet"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10448,8 +10386,8 @@
   <autoFilter ref="A1:C5" xr:uid="{44046314-B45D-4FBD-AB59-40E215828895}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3D76B09E-61B3-48CE-8430-EA93A493F6D4}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{7E5DC835-FA63-49B4-9E41-63B34787F5F9}" name="Price ($)" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{6DF38014-2A3F-48C0-AFD1-C97F0DA9FAC4}" name="Units Sold" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{7E5DC835-FA63-49B4-9E41-63B34787F5F9}" name="Price ($)"/>
+    <tableColumn id="3" xr3:uid="{6DF38014-2A3F-48C0-AFD1-C97F0DA9FAC4}" name="Units Sold"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10460,7 +10398,7 @@
   <autoFilter ref="A1:B5" xr:uid="{854184C0-11BE-470B-9AAE-8D996C01FD75}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{93981815-9F52-44D0-B0AD-000D0A261264}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{52CBAC57-9BC2-4F24-95F2-2570BC7F99AF}" name="Budget" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{52CBAC57-9BC2-4F24-95F2-2570BC7F99AF}" name="Budget"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10471,10 +10409,10 @@
   <autoFilter ref="A1:E3" xr:uid="{BFD98620-53F4-4A7B-917E-2F2D07544F17}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{25E65101-623A-4E97-9D4F-C991AF81A253}" name="Quarter"/>
-    <tableColumn id="2" xr3:uid="{C866BA2B-9180-4651-95FF-9AF2EA1AA03B}" name="Electronics" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{000C1675-EE8A-48C7-A119-17BD973C3F4B}" name="Clothing" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{589F7E3E-A5A7-4C98-8453-7D82E0E107A7}" name="Food" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{6D414AF1-3518-45F2-BC6C-DAAA0B7DE738}" name="Home" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{C866BA2B-9180-4651-95FF-9AF2EA1AA03B}" name="Electronics"/>
+    <tableColumn id="3" xr3:uid="{000C1675-EE8A-48C7-A119-17BD973C3F4B}" name="Clothing"/>
+    <tableColumn id="4" xr3:uid="{589F7E3E-A5A7-4C98-8453-7D82E0E107A7}" name="Food"/>
+    <tableColumn id="5" xr3:uid="{6D414AF1-3518-45F2-BC6C-DAAA0B7DE738}" name="Home"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10484,9 +10422,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{EA414483-F9F2-4B7E-B644-37C58CF9DDFA}" name="ComboChartTable" displayName="ComboChartTable" ref="A1:C4" totalsRowShown="0">
   <autoFilter ref="A1:C4" xr:uid="{EA414483-F9F2-4B7E-B644-37C58CF9DDFA}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8646F911-3A34-4300-BA20-C9CC02C005D1}" name="Date" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{7417EAA7-6F9C-4AFC-A5E9-2EBA455D02B3}" name="Revenue" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{67872E29-B587-4821-8CF2-1DF062546030}" name="Growth Rate" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8646F911-3A34-4300-BA20-C9CC02C005D1}" name="Date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{7417EAA7-6F9C-4AFC-A5E9-2EBA455D02B3}" name="Revenue"/>
+    <tableColumn id="3" xr3:uid="{67872E29-B587-4821-8CF2-1DF062546030}" name="Growth Rate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10776,7 +10714,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="2">
@@ -10793,7 +10731,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="2">
@@ -10810,7 +10748,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="2">
@@ -10859,7 +10797,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="2">
@@ -10867,7 +10805,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="2">
@@ -10875,7 +10813,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B4" s="2">
@@ -10883,7 +10821,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="2">
@@ -11038,7 +10976,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="1">
@@ -11046,7 +10984,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="1">
@@ -11054,7 +10992,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="1">
@@ -11062,7 +11000,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B5" s="1">
@@ -11102,7 +11040,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="2">
@@ -11110,7 +11048,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="2">
@@ -11118,7 +11056,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="2">
@@ -11172,7 +11110,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="2">
@@ -11186,7 +11124,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="2">
@@ -11200,7 +11138,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B4" s="2">
@@ -11214,7 +11152,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="2">
@@ -11278,7 +11216,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="2">
@@ -11289,7 +11227,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="2">
@@ -11300,7 +11238,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B4" s="2">
@@ -11311,7 +11249,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="2">
@@ -11371,7 +11309,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2">
@@ -11379,7 +11317,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2">
@@ -11387,7 +11325,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="2">
@@ -11395,7 +11333,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B5" s="2">
@@ -11445,7 +11383,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B2" s="2">
@@ -11462,7 +11400,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="2">
